--- a/output/pdf_financials_xlsx/GTC.xlsx
+++ b/output/pdf_financials_xlsx/GTC.xlsx
@@ -5953,11 +5953,11 @@
         <v>1.204025</v>
       </c>
       <c r="D92" s="3" t="n">
+        <v>1.204025</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>1.23243</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
       </c>
@@ -5989,10 +5989,10 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.133923</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.173196</v>
       </c>
     </row>
     <row r="93">
@@ -7529,10 +7529,10 @@
         <v>-0.09023200000000001</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.040192</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01384</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>-0.064763</v>
@@ -10190,7 +10190,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -17340,7 +17344,11 @@
           <t>Reserves (Note 14) 1,235,494</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -27776,7 +27784,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GTC.xlsx
+++ b/output/pdf_financials_xlsx/GTC.xlsx
@@ -1103,25 +1103,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000373</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001047</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000259</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000373</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000293</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000137</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000121</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000106</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001752</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000247</v>
       </c>
     </row>
     <row r="13">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.306899</v>
+        <v>-0.307272</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.143921</v>
+        <v>-0.144968</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.270534</v>
+        <v>-0.270793</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.196865</v>
+        <v>-0.197238</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.50118</v>
+        <v>-0.5014729999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.503042</v>
+        <v>-0.503343</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.304994</v>
+        <v>-0.305131</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.329166</v>
+        <v>-0.329287</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.328462</v>
+        <v>-0.328568</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.449974</v>
+        <v>-0.451726</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.451381</v>
+        <v>-0.451626</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.772365</v>
+        <v>-0.772612</v>
       </c>
     </row>
     <row r="28">
@@ -2286,25 +2286,25 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.306004</v>
+        <v>-0.306377</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.143015</v>
+        <v>-0.144062</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.269653</v>
+        <v>-0.269912</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.196281</v>
+        <v>-0.196654</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.500792</v>
+        <v>-0.501085</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.502759</v>
+        <v>-0.50306</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.304733</v>
+        <v>-0.30487</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.329113</v>
+        <v>-0.329234</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.328421</v>
+        <v>-0.328527</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.44994</v>
+        <v>-0.451692</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.451355</v>
+        <v>-0.4516</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.772343</v>
+        <v>-0.77259</v>
       </c>
     </row>
     <row r="30">
@@ -2589,46 +2589,46 @@
         <v>0.294722</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.294722</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.066272</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.14503</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.038135</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.093351</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010564</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.073602</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006904</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.009497999999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.113509</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.005652</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.064333</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.338773</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.150065</v>
       </c>
     </row>
     <row r="35">
@@ -2699,46 +2699,46 @@
         <v>0.294722</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.294722</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.066272</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.14503</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.038135</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.093351</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010564</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.073602</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006904</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.009497999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.113509</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.005652</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.064333</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.338773</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.150065</v>
       </c>
     </row>
     <row r="37">
@@ -3359,46 +3359,46 @@
         <v>0.017993</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.312715</v>
+        <v>0.017993</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.403503</v>
+        <v>0.337231</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.146361</v>
+        <v>0.001331</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.039512</v>
+        <v>0.001377</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.094774</v>
+        <v>0.001423</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.01449</v>
+        <v>0.003926</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.011695</v>
+        <v>0.004791</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.01461</v>
+        <v>0.005112</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.124214</v>
+        <v>0.010705</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.018961</v>
+        <v>0.013309</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.075049</v>
+        <v>0.010716</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.349162</v>
+        <v>0.010389</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.154108</v>
+        <v>0.004043</v>
       </c>
     </row>
     <row r="49">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -32892,7 +32892,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -34278,7 +34278,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -35328,7 +35328,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -37154,7 +37154,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
